--- a/ConfigExporter/xlsx/ogs_config.xlsx
+++ b/ConfigExporter/xlsx/ogs_config.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -742,49 +742,66 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>defaultBotGameBoardSize</t>
+          <t>automatchReceiveMilliseconds</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Default OGS bot game board size</t>
+          <t>Automatch receive timeout in milliseconds</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>defaultBotGameRules</t>
+          <t>defaultBotGameBoardSize</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Default OGS bot game rules</t>
+          <t>Default OGS bot game board size</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>japanese</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>defaultBotGameRules</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Default OGS bot game rules</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>japanese</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>defaultBotGameName</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Default OGS bot game name</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Friendly Match</t>
         </is>
